--- a/data/3.meta_data/meta_data/metadata.xlsx
+++ b/data/3.meta_data/meta_data/metadata.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HQO27"/>
+  <dimension ref="A1:HRE28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -29687,6 +29687,86 @@
           <t>cognitivereappraisalskill_emotionalreflectionskill</t>
         </is>
       </c>
+      <c r="HQP1" s="1" t="inlineStr">
+        <is>
+          <t>academicachievement_academicburnout</t>
+        </is>
+      </c>
+      <c r="HQQ1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_sex</t>
+        </is>
+      </c>
+      <c r="HQR1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_selfmanagement</t>
+        </is>
+      </c>
+      <c r="HQS1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_innovation</t>
+        </is>
+      </c>
+      <c r="HQT1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_cooperation</t>
+        </is>
+      </c>
+      <c r="HQU1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_socialengagement</t>
+        </is>
+      </c>
+      <c r="HQV1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_emotionalresilience</t>
+        </is>
+      </c>
+      <c r="HQW1" s="1" t="inlineStr">
+        <is>
+          <t>academicengagement_academicselfefficacy</t>
+        </is>
+      </c>
+      <c r="HQX1" s="1" t="inlineStr">
+        <is>
+          <t>academicengagement_srlstrategies</t>
+        </is>
+      </c>
+      <c r="HQY1" s="1" t="inlineStr">
+        <is>
+          <t>academicengagement_academicsatisfaction</t>
+        </is>
+      </c>
+      <c r="HQZ1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_academicengagement</t>
+        </is>
+      </c>
+      <c r="HRA1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_academicselfefficacy</t>
+        </is>
+      </c>
+      <c r="HRB1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_srlstrategies</t>
+        </is>
+      </c>
+      <c r="HRC1" s="1" t="inlineStr">
+        <is>
+          <t>academicsatisfaction_satisfactionwithlife</t>
+        </is>
+      </c>
+      <c r="HRD1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_academicsatisfaction</t>
+        </is>
+      </c>
+      <c r="HRE1" s="1" t="inlineStr">
+        <is>
+          <t>academicburnout_satisfactionwithlife</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -84887,6 +84967,376 @@
       </c>
       <c r="HQO27">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0100a</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10.1177/00222194261417592</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>JOURNAL OF LEARNING DISABILITIES</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Pellegrino et al.</t>
+        </is>
+      </c>
+      <c r="K28">
+        <v>2026</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>academicachievement; schoolsatisfaction; disabilities</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>gerardo.pellegrino@phd.unipd.it</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://osf.io/69q84/</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="V28">
+        <v>752</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>young_adult</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>learning disabilities</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="AF28">
+        <v>0.3897922881894729</v>
+      </c>
+      <c r="AG28">
+        <v>0.4343885218477122</v>
+      </c>
+      <c r="AH28">
+        <v>0.365121009514038</v>
+      </c>
+      <c r="AI28">
+        <v>0.2636812289743455</v>
+      </c>
+      <c r="AO28">
+        <v>0.4573981796399659</v>
+      </c>
+      <c r="AP28">
+        <v>0.2150884111587807</v>
+      </c>
+      <c r="AY28">
+        <v>0.309149417263011</v>
+      </c>
+      <c r="AZ28">
+        <v>0.5658514819150465</v>
+      </c>
+      <c r="BA28">
+        <v>0.4043396359654297</v>
+      </c>
+      <c r="BB28">
+        <v>0.4387692360844135</v>
+      </c>
+      <c r="BH28">
+        <v>0.3772889514539913</v>
+      </c>
+      <c r="BI28">
+        <v>0.08903509188091555</v>
+      </c>
+      <c r="BR28">
+        <v>0.3542830877811803</v>
+      </c>
+      <c r="BS28">
+        <v>0.5126122080478571</v>
+      </c>
+      <c r="BT28">
+        <v>0.3822180284555047</v>
+      </c>
+      <c r="BZ28">
+        <v>0.4067922354760057</v>
+      </c>
+      <c r="CA28">
+        <v>0.1223279872174429</v>
+      </c>
+      <c r="CJ28">
+        <v>0.2629075583679749</v>
+      </c>
+      <c r="CK28">
+        <v>0.3565627585032196</v>
+      </c>
+      <c r="CQ28">
+        <v>0.3184101560380294</v>
+      </c>
+      <c r="CR28">
+        <v>0.06861347542171189</v>
+      </c>
+      <c r="DA28">
+        <v>0.4503350402683908</v>
+      </c>
+      <c r="DG28">
+        <v>0.2153874357713632</v>
+      </c>
+      <c r="DH28">
+        <v>-0.007065551422642442</v>
+      </c>
+      <c r="DQ28">
+        <v>0.1375828062149693</v>
+      </c>
+      <c r="GE28">
+        <v>0.201815379344535</v>
+      </c>
+      <c r="GN28">
+        <v>0.4657733418003734</v>
+      </c>
+      <c r="GW28">
+        <v>0.07828991508347706</v>
+      </c>
+      <c r="JN28">
+        <v>0.1093216055628479</v>
+      </c>
+      <c r="JO28">
+        <v>-0.08373713535117611</v>
+      </c>
+      <c r="JP28">
+        <v>0.07883443083303709</v>
+      </c>
+      <c r="JQ28">
+        <v>-0.04096254386167063</v>
+      </c>
+      <c r="JR28">
+        <v>-0.164617946223372</v>
+      </c>
+      <c r="JS28">
+        <v>0.03661715191468676</v>
+      </c>
+      <c r="JT28">
+        <v>0.1761651852528344</v>
+      </c>
+      <c r="DWY28">
+        <v>0.1691472847032733</v>
+      </c>
+      <c r="HKD28">
+        <v>0.5190585096777481</v>
+      </c>
+      <c r="HKF28">
+        <v>0.5175109381568147</v>
+      </c>
+      <c r="HKH28">
+        <v>0.2173495938924325</v>
+      </c>
+      <c r="HKJ28">
+        <v>0.2231156696041342</v>
+      </c>
+      <c r="HKL28">
+        <v>0.308283191116604</v>
+      </c>
+      <c r="HKN28">
+        <v>0.2420030344806121</v>
+      </c>
+      <c r="HKQ28">
+        <v>0.1020337966898319</v>
+      </c>
+      <c r="HLI28">
+        <v>0.06298995314517195</v>
+      </c>
+      <c r="HLM28">
+        <v>0.5659781083300155</v>
+      </c>
+      <c r="HLQ28">
+        <v>0.3133153878823099</v>
+      </c>
+      <c r="HLU28">
+        <v>0.3128176562091499</v>
+      </c>
+      <c r="HLY28">
+        <v>0.3487956190236833</v>
+      </c>
+      <c r="HMC28">
+        <v>0.31658358416447</v>
+      </c>
+      <c r="HMO28">
+        <v>0.3074950168848075</v>
+      </c>
+      <c r="HMQ28">
+        <v>0.5312753669005742</v>
+      </c>
+      <c r="HND28">
+        <v>0.2772002425663024</v>
+      </c>
+      <c r="HNH28">
+        <v>0.259628994844297</v>
+      </c>
+      <c r="HNJ28">
+        <v>0.303601934935523</v>
+      </c>
+      <c r="HNK28">
+        <v>0.3005495330136056</v>
+      </c>
+      <c r="HNL28">
+        <v>0.2756542090471613</v>
+      </c>
+      <c r="HNM28">
+        <v>0.2156124607101731</v>
+      </c>
+      <c r="HNN28">
+        <v>0.2826184237158135</v>
+      </c>
+      <c r="HNO28">
+        <v>0.2769187898730788</v>
+      </c>
+      <c r="HNP28">
+        <v>0.2309571978689031</v>
+      </c>
+      <c r="HNQ28">
+        <v>0.1112902803236752</v>
+      </c>
+      <c r="HNR28">
+        <v>0.0003824779547645992</v>
+      </c>
+      <c r="HQP28">
+        <v>-0.1192946976461384</v>
+      </c>
+      <c r="HQQ28">
+        <v>0.05242883361164581</v>
+      </c>
+      <c r="HQR28">
+        <v>-0.2766343722339456</v>
+      </c>
+      <c r="HQS28">
+        <v>-0.1814312710539319</v>
+      </c>
+      <c r="HQT28">
+        <v>-0.1694009206403628</v>
+      </c>
+      <c r="HQU28">
+        <v>-0.2209096192298554</v>
+      </c>
+      <c r="HQV28">
+        <v>-0.3855928647410115</v>
+      </c>
+      <c r="HQW28">
+        <v>0.4612713330315539</v>
+      </c>
+      <c r="HQX28">
+        <v>0.4425697766589992</v>
+      </c>
+      <c r="HQY28">
+        <v>0.5520892997190852</v>
+      </c>
+      <c r="HQZ28">
+        <v>-0.4757545371340873</v>
+      </c>
+      <c r="HRA28">
+        <v>-0.3750050994964406</v>
+      </c>
+      <c r="HRB28">
+        <v>-0.2988773805863365</v>
+      </c>
+      <c r="HRC28">
+        <v>0.3736792622798559</v>
+      </c>
+      <c r="HRD28">
+        <v>-0.4597814935732237</v>
+      </c>
+      <c r="HRE28">
+        <v>-0.4130474373501075</v>
       </c>
     </row>
   </sheetData>

--- a/data/3.meta_data/meta_data/metadata.xlsx
+++ b/data/3.meta_data/meta_data/metadata.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HRE28"/>
+  <dimension ref="A1:HRE29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -84971,11 +84971,11 @@
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0100</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -84985,37 +84985,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0100a</t>
+          <t>0095a</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.1177/00222194261417592</t>
+          <t>10.1016/j.jrp.2026.104705</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
+          <t>Experiental features of volunteering predict changes in college students' social, emotional, and behavioral skills</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
+          <t>Using an exploratory quasi-experimental design, the present research investigated SEB skills as an antecedent and consequence of volunteering in a sample of college students who were either actively volunteering (N = 169) or not (N = 286). Results indicated that more skilled students participated in volunteering, but volunteering, in general, did not predict positive SEB skill change. However, participants who reported interacting with others while volunteering experienced growth in socially relevant skills. Participants who reported positive subjective evaluations of volunteering also experienced growth in several SEB skills. These findings suggest that domain relevant actions, as well as subjective experiences of engaging in those actions, may be critical for positive SEB skill development. Â© 2026 Elsevier Inc.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>JOURNAL OF LEARNING DISABILITIES</t>
+          <t>Journal of Research in Personality</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
+          <t>Sewell, Madison N. and Napolitano, Christopher M. and Yoon, Heejun and Soto, Christopher John and Roberts, Brent W.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Pellegrino et al.</t>
+          <t>Sewell et al.</t>
         </is>
       </c>
       <c r="K28">
@@ -85033,309 +85033,498 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
+          <t>volunteering; skilldevelopment</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://osf.io/wsvxt/</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>59.8</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="V28">
+        <v>455</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>young_adult</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="AF28">
+        <v>0.3330224193081219</v>
+      </c>
+      <c r="AG28">
+        <v>0.4596512270598077</v>
+      </c>
+      <c r="AH28">
+        <v>0.5320576831334216</v>
+      </c>
+      <c r="AI28">
+        <v>0.3242378668410512</v>
+      </c>
+      <c r="AZ28">
+        <v>0.4979522039905168</v>
+      </c>
+      <c r="BA28">
+        <v>0.3652453106055803</v>
+      </c>
+      <c r="BB28">
+        <v>0.387208368782807</v>
+      </c>
+      <c r="BS28">
+        <v>0.4613724415274998</v>
+      </c>
+      <c r="BT28">
+        <v>0.4106499312594121</v>
+      </c>
+      <c r="CK28">
+        <v>0.3478894084815676</v>
+      </c>
+      <c r="JN28">
+        <v>0.04455123620056217</v>
+      </c>
+      <c r="JO28">
+        <v>0.07530718858853158</v>
+      </c>
+      <c r="JP28">
+        <v>0.1418991528525441</v>
+      </c>
+      <c r="JQ28">
+        <v>0.02259557439649528</v>
+      </c>
+      <c r="JR28">
+        <v>-0.1812978912538156</v>
+      </c>
+      <c r="DLS28">
+        <v>-0.05125524187103325</v>
+      </c>
+      <c r="DMM28">
+        <v>0.2646806101192998</v>
+      </c>
+      <c r="DNA28">
+        <v>0.07878029097361108</v>
+      </c>
+      <c r="DNO28">
+        <v>0.1666545203436967</v>
+      </c>
+      <c r="DOC28">
+        <v>0.1772218757143176</v>
+      </c>
+      <c r="DOQ28">
+        <v>0.115134156294775</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0100a</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10.1177/00222194261417592</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>JOURNAL OF LEARNING DISABILITIES</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Pellegrino et al.</t>
+        </is>
+      </c>
+      <c r="K29">
+        <v>2026</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
           <t>academicachievement; schoolsatisfaction; disabilities</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>gerardo.pellegrino@phd.unipd.it</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>https://osf.io/69q84/</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>cross</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>22.28</t>
         </is>
       </c>
-      <c r="V28">
+      <c r="V29">
         <v>752</v>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>young_adult</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>clinical</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>learning disabilities</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>bessi45</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>TF</t>
         </is>
       </c>
-      <c r="AF28">
+      <c r="AF29">
         <v>0.3897922881894729</v>
       </c>
-      <c r="AG28">
+      <c r="AG29">
         <v>0.4343885218477122</v>
       </c>
-      <c r="AH28">
+      <c r="AH29">
         <v>0.365121009514038</v>
       </c>
-      <c r="AI28">
+      <c r="AI29">
         <v>0.2636812289743455</v>
       </c>
-      <c r="AO28">
+      <c r="AO29">
         <v>0.4573981796399659</v>
       </c>
-      <c r="AP28">
+      <c r="AP29">
         <v>0.2150884111587807</v>
       </c>
-      <c r="AY28">
+      <c r="AY29">
         <v>0.309149417263011</v>
       </c>
-      <c r="AZ28">
+      <c r="AZ29">
         <v>0.5658514819150465</v>
       </c>
-      <c r="BA28">
+      <c r="BA29">
         <v>0.4043396359654297</v>
       </c>
-      <c r="BB28">
+      <c r="BB29">
         <v>0.4387692360844135</v>
       </c>
-      <c r="BH28">
+      <c r="BH29">
         <v>0.3772889514539913</v>
       </c>
-      <c r="BI28">
+      <c r="BI29">
         <v>0.08903509188091555</v>
       </c>
-      <c r="BR28">
+      <c r="BR29">
         <v>0.3542830877811803</v>
       </c>
-      <c r="BS28">
+      <c r="BS29">
         <v>0.5126122080478571</v>
       </c>
-      <c r="BT28">
+      <c r="BT29">
         <v>0.3822180284555047</v>
       </c>
-      <c r="BZ28">
+      <c r="BZ29">
         <v>0.4067922354760057</v>
       </c>
-      <c r="CA28">
+      <c r="CA29">
         <v>0.1223279872174429</v>
       </c>
-      <c r="CJ28">
+      <c r="CJ29">
         <v>0.2629075583679749</v>
       </c>
-      <c r="CK28">
+      <c r="CK29">
         <v>0.3565627585032196</v>
       </c>
-      <c r="CQ28">
+      <c r="CQ29">
         <v>0.3184101560380294</v>
       </c>
-      <c r="CR28">
+      <c r="CR29">
         <v>0.06861347542171189</v>
       </c>
-      <c r="DA28">
+      <c r="DA29">
         <v>0.4503350402683908</v>
       </c>
-      <c r="DG28">
+      <c r="DG29">
         <v>0.2153874357713632</v>
       </c>
-      <c r="DH28">
+      <c r="DH29">
         <v>-0.007065551422642442</v>
       </c>
-      <c r="DQ28">
+      <c r="DQ29">
         <v>0.1375828062149693</v>
       </c>
-      <c r="GE28">
+      <c r="GE29">
         <v>0.201815379344535</v>
       </c>
-      <c r="GN28">
+      <c r="GN29">
         <v>0.4657733418003734</v>
       </c>
-      <c r="GW28">
+      <c r="GW29">
         <v>0.07828991508347706</v>
       </c>
-      <c r="JN28">
+      <c r="JN29">
         <v>0.1093216055628479</v>
       </c>
-      <c r="JO28">
+      <c r="JO29">
         <v>-0.08373713535117611</v>
       </c>
-      <c r="JP28">
+      <c r="JP29">
         <v>0.07883443083303709</v>
       </c>
-      <c r="JQ28">
+      <c r="JQ29">
         <v>-0.04096254386167063</v>
       </c>
-      <c r="JR28">
+      <c r="JR29">
         <v>-0.164617946223372</v>
       </c>
-      <c r="JS28">
+      <c r="JS29">
         <v>0.03661715191468676</v>
       </c>
-      <c r="JT28">
+      <c r="JT29">
         <v>0.1761651852528344</v>
       </c>
-      <c r="DWY28">
+      <c r="DWY29">
         <v>0.1691472847032733</v>
       </c>
-      <c r="HKD28">
+      <c r="HKD29">
         <v>0.5190585096777481</v>
       </c>
-      <c r="HKF28">
+      <c r="HKF29">
         <v>0.5175109381568147</v>
       </c>
-      <c r="HKH28">
+      <c r="HKH29">
         <v>0.2173495938924325</v>
       </c>
-      <c r="HKJ28">
+      <c r="HKJ29">
         <v>0.2231156696041342</v>
       </c>
-      <c r="HKL28">
+      <c r="HKL29">
         <v>0.308283191116604</v>
       </c>
-      <c r="HKN28">
+      <c r="HKN29">
         <v>0.2420030344806121</v>
       </c>
-      <c r="HKQ28">
+      <c r="HKQ29">
         <v>0.1020337966898319</v>
       </c>
-      <c r="HLI28">
+      <c r="HLI29">
         <v>0.06298995314517195</v>
       </c>
-      <c r="HLM28">
+      <c r="HLM29">
         <v>0.5659781083300155</v>
       </c>
-      <c r="HLQ28">
+      <c r="HLQ29">
         <v>0.3133153878823099</v>
       </c>
-      <c r="HLU28">
+      <c r="HLU29">
         <v>0.3128176562091499</v>
       </c>
-      <c r="HLY28">
+      <c r="HLY29">
         <v>0.3487956190236833</v>
       </c>
-      <c r="HMC28">
+      <c r="HMC29">
         <v>0.31658358416447</v>
       </c>
-      <c r="HMO28">
+      <c r="HMO29">
         <v>0.3074950168848075</v>
       </c>
-      <c r="HMQ28">
+      <c r="HMQ29">
         <v>0.5312753669005742</v>
       </c>
-      <c r="HND28">
+      <c r="HND29">
         <v>0.2772002425663024</v>
       </c>
-      <c r="HNH28">
+      <c r="HNH29">
         <v>0.259628994844297</v>
       </c>
-      <c r="HNJ28">
+      <c r="HNJ29">
         <v>0.303601934935523</v>
       </c>
-      <c r="HNK28">
+      <c r="HNK29">
         <v>0.3005495330136056</v>
       </c>
-      <c r="HNL28">
+      <c r="HNL29">
         <v>0.2756542090471613</v>
       </c>
-      <c r="HNM28">
+      <c r="HNM29">
         <v>0.2156124607101731</v>
       </c>
-      <c r="HNN28">
+      <c r="HNN29">
         <v>0.2826184237158135</v>
       </c>
-      <c r="HNO28">
+      <c r="HNO29">
         <v>0.2769187898730788</v>
       </c>
-      <c r="HNP28">
+      <c r="HNP29">
         <v>0.2309571978689031</v>
       </c>
-      <c r="HNQ28">
+      <c r="HNQ29">
         <v>0.1112902803236752</v>
       </c>
-      <c r="HNR28">
+      <c r="HNR29">
         <v>0.0003824779547645992</v>
       </c>
-      <c r="HQP28">
+      <c r="HQP29">
         <v>-0.1192946976461384</v>
       </c>
-      <c r="HQQ28">
+      <c r="HQQ29">
         <v>0.05242883361164581</v>
       </c>
-      <c r="HQR28">
+      <c r="HQR29">
         <v>-0.2766343722339456</v>
       </c>
-      <c r="HQS28">
+      <c r="HQS29">
         <v>-0.1814312710539319</v>
       </c>
-      <c r="HQT28">
+      <c r="HQT29">
         <v>-0.1694009206403628</v>
       </c>
-      <c r="HQU28">
+      <c r="HQU29">
         <v>-0.2209096192298554</v>
       </c>
-      <c r="HQV28">
+      <c r="HQV29">
         <v>-0.3855928647410115</v>
       </c>
-      <c r="HQW28">
+      <c r="HQW29">
         <v>0.4612713330315539</v>
       </c>
-      <c r="HQX28">
+      <c r="HQX29">
         <v>0.4425697766589992</v>
       </c>
-      <c r="HQY28">
+      <c r="HQY29">
         <v>0.5520892997190852</v>
       </c>
-      <c r="HQZ28">
+      <c r="HQZ29">
         <v>-0.4757545371340873</v>
       </c>
-      <c r="HRA28">
+      <c r="HRA29">
         <v>-0.3750050994964406</v>
       </c>
-      <c r="HRB28">
+      <c r="HRB29">
         <v>-0.2988773805863365</v>
       </c>
-      <c r="HRC28">
+      <c r="HRC29">
         <v>0.3736792622798559</v>
       </c>
-      <c r="HRD28">
+      <c r="HRD29">
         <v>-0.4597814935732237</v>
       </c>
-      <c r="HRE28">
+      <c r="HRE29">
         <v>-0.4130474373501075</v>
       </c>
     </row>

--- a/data/3.meta_data/meta_data/metadata.xlsx
+++ b/data/3.meta_data/meta_data/metadata.xlsx
@@ -84990,7 +84990,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10.1016/j.jrp.2026.104705</t>
+          <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -85179,7 +85179,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10.1177/00222194261417592</t>
+          <t>https://doi.org/10.1177/00222194261417592</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">

--- a/data/3.meta_data/meta_data/metadata.xlsx
+++ b/data/3.meta_data/meta_data/metadata.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:HRE29"/>
+  <dimension ref="A1:HRE27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -84075,11 +84075,11 @@
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0080</t>
+          <t>0087</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -84089,37 +84089,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0080a</t>
+          <t>0087a</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpsyg.2025.1653072</t>
+          <t>https://doi.org/10.1007/s11218-025-10079-9</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Undergraduates' achievement and satisfaction: the role of study-related factors and soft skills</t>
+          <t>Autonomy support and studentsâ€™ perceived social-emotional competence: predicting parent-reported social-emotional skills</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The present study tested a comprehensive model in which five social, emotional, and behavioral (SEB) skill domains (self-management, social engagement, cooperation, emotional resilience, and innovation</t>
+          <t>In this study, we investigated perceived social-emotional competence (PSEC) among 373 Australian secondary school students in relation to parent ratings of social-emotional skills, and perceived teacher and parental autonomy support. Using bifactor exploratory structural equation modelling, we examined five dimensions of PSEC (perceived competence for assertiveness, tolerance, social regulation, emotion regulation, and emotional awareness), identifying a global factor and five specific factors. Following that, we employed structural equation modelling to investigate links between these global and specific factors and five parent-reported social-emotional skills: leadership, cultural competence, teamwork, cognitive reappraisal, and capacity for emotional reflection. Global PSEC was associated positively with all skills, whereas the specific factors were, with one exception, each associated with greater parent-rated skill in a corresponding area (e.g., assertiveness with greater leadership skill; emotion awareness with reflective skills). Addressing a second aim of the research, we tested the extent to which students’ perceptions of autonomy support from teachers and parents assessed near the start of a school term were associated with both students’ PSEC and parent-rated skills assessed at the end of the term. Autonomy-supportive parenting was positively associated with global PSEC. Autonomy-supportive teaching was associated with greater levels of two specific factors: perceived competence for assertiveness and social regulation. Together, findings hold relevance to knowledge and efforts aimed at enhancing social-emotional skills among students.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Frontiers in Psychology</t>
+          <t>Social Psychology of Education</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sharabi, Adi and Carretti, Barbara and Cueli, Marisol Soledad and RodrÃ­guez PÃ©rez, Celestino and Pellegrino, Gerardo</t>
+          <t>Collie, Rebecca J. and Ryan, Richard M.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sharabi et al.</t>
+          <t>Collie &amp; Ryan</t>
         </is>
       </c>
       <c r="K25">
@@ -84130,14 +84130,9 @@
           <t>include</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>positiveschooloutcomes; academicachievement; learningfactors</t>
+          <t>autonomysupport</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -84147,7 +84142,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>adi.sharabi@smkb.ac.il</t>
+          <t>rebecca.collie@unsw.edu.au</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -84162,25 +84157,25 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>51</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>22.74</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V25">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>young_adult</t>
+          <t>school_age</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -84190,7 +84185,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>bessi20</t>
+          <t>bessi_otherReport</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -84203,149 +84198,203 @@
           <t>TF</t>
         </is>
       </c>
-      <c r="AF25">
-        <v>0.4987536058562987</v>
-      </c>
-      <c r="AG25">
-        <v>0.4112158902189516</v>
-      </c>
-      <c r="AH25">
-        <v>0.4630780298543363</v>
-      </c>
-      <c r="AI25">
-        <v>0.4887643784498452</v>
-      </c>
-      <c r="AP25">
-        <v>0.4097496698568251</v>
-      </c>
-      <c r="AZ25">
-        <v>0.6063934495806812</v>
-      </c>
-      <c r="BA25">
-        <v>0.4737777442999984</v>
-      </c>
-      <c r="BB25">
-        <v>0.517252995752813</v>
-      </c>
-      <c r="BI25">
-        <v>0.3339854401853342</v>
-      </c>
-      <c r="BS25">
-        <v>0.6119387520279144</v>
-      </c>
-      <c r="BT25">
-        <v>0.4713173325255526</v>
-      </c>
-      <c r="CA25">
-        <v>0.2968543677387699</v>
-      </c>
-      <c r="CK25">
-        <v>0.5528025598544609</v>
-      </c>
-      <c r="CR25">
-        <v>0.2613720888626943</v>
-      </c>
-      <c r="DH25">
-        <v>0.2449879959536252</v>
-      </c>
-      <c r="JN25">
-        <v>0.07540136124880159</v>
-      </c>
-      <c r="JO25">
-        <v>-0.05489924897864821</v>
-      </c>
-      <c r="JP25">
-        <v>0.07314249017970333</v>
-      </c>
-      <c r="JQ25">
-        <v>0.02295711992983375</v>
-      </c>
-      <c r="JR25">
-        <v>-0.1101763000383637</v>
-      </c>
-      <c r="JT25">
-        <v>0.1099683433260414</v>
-      </c>
-      <c r="HKD25">
-        <v>0.5130449408120934</v>
-      </c>
-      <c r="HKF25">
-        <v>0.5957502994256506</v>
-      </c>
-      <c r="HKH25">
-        <v>0.4037893824882295</v>
-      </c>
-      <c r="HKJ25">
-        <v>0.4132392379259404</v>
-      </c>
-      <c r="HKL25">
-        <v>0.5099288031117473</v>
-      </c>
-      <c r="HKN25">
-        <v>0.3930905978301036</v>
-      </c>
-      <c r="HKQ25">
-        <v>0.04835137891372377</v>
-      </c>
-      <c r="HLI25">
-        <v>0.04645758107183325</v>
-      </c>
-      <c r="HLM25">
-        <v>0.4347691948229001</v>
-      </c>
-      <c r="HLQ25">
-        <v>0.3225309986068023</v>
-      </c>
-      <c r="HLU25">
-        <v>0.2200361070098487</v>
-      </c>
-      <c r="HLY25">
-        <v>0.3413427741827634</v>
-      </c>
-      <c r="HMC25">
-        <v>0.2266590082419102</v>
-      </c>
-      <c r="HMQ25">
-        <v>0.4678753950824326</v>
-      </c>
-      <c r="HND25">
-        <v>0.2808780128533402</v>
-      </c>
-      <c r="HNJ25">
-        <v>0.3251826833125769</v>
-      </c>
-      <c r="HNK25">
-        <v>0.4165522501235401</v>
-      </c>
-      <c r="HNL25">
-        <v>0.3218670586777202</v>
-      </c>
-      <c r="HNM25">
-        <v>0.3429729815611784</v>
-      </c>
-      <c r="HNN25">
-        <v>0.287941989686476</v>
-      </c>
-      <c r="HNO25">
-        <v>0.2666184161153234</v>
-      </c>
-      <c r="HNP25">
-        <v>0.3325938421307833</v>
-      </c>
-      <c r="HNQ25">
-        <v>0.1412995898511461</v>
-      </c>
-      <c r="HNR25">
-        <v>0.02477904180121925</v>
+      <c r="YX25">
+        <v>0.71</v>
+      </c>
+      <c r="ZA25">
+        <v>0.45</v>
+      </c>
+      <c r="ACQ25">
+        <v>0.73</v>
+      </c>
+      <c r="HNS25">
+        <v>0.46</v>
+      </c>
+      <c r="HNT25">
+        <v>0.31</v>
+      </c>
+      <c r="HNU25">
+        <v>0.25</v>
+      </c>
+      <c r="HNV25">
+        <v>0.1</v>
+      </c>
+      <c r="HNW25">
+        <v>0.31</v>
+      </c>
+      <c r="HNX25">
+        <v>0.14</v>
+      </c>
+      <c r="HNY25">
+        <v>0.08</v>
+      </c>
+      <c r="HNZ25">
+        <v>0.22</v>
+      </c>
+      <c r="HOA25">
+        <v>0.22</v>
+      </c>
+      <c r="HOB25">
+        <v>0.36</v>
+      </c>
+      <c r="HOC25">
+        <v>0.32</v>
+      </c>
+      <c r="HOD25">
+        <v>0.25</v>
+      </c>
+      <c r="HOE25">
+        <v>0.47</v>
+      </c>
+      <c r="HOF25">
+        <v>0.05</v>
+      </c>
+      <c r="HOG25">
+        <v>0.13</v>
+      </c>
+      <c r="HOH25">
+        <v>0.13</v>
+      </c>
+      <c r="HOI25">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="HOJ25">
+        <v>0.12</v>
+      </c>
+      <c r="HOK25">
+        <v>0.35</v>
+      </c>
+      <c r="HOL25">
+        <v>0.41</v>
+      </c>
+      <c r="HOM25">
+        <v>0.52</v>
+      </c>
+      <c r="HON25">
+        <v>0.39</v>
+      </c>
+      <c r="HOO25">
+        <v>0.42</v>
+      </c>
+      <c r="HOU25">
+        <v>0.59</v>
+      </c>
+      <c r="HOV25">
+        <v>0.5</v>
+      </c>
+      <c r="HOW25">
+        <v>0.72</v>
+      </c>
+      <c r="HOX25">
+        <v>0.63</v>
+      </c>
+      <c r="HOY25">
+        <v>0.65</v>
+      </c>
+      <c r="HPD25">
+        <v>0.37</v>
+      </c>
+      <c r="HPE25">
+        <v>0.04</v>
+      </c>
+      <c r="HPF25">
+        <v>0.12</v>
+      </c>
+      <c r="HPG25">
+        <v>0.09</v>
+      </c>
+      <c r="HPH25">
+        <v>-0.01</v>
+      </c>
+      <c r="HPL25">
+        <v>-0.05</v>
+      </c>
+      <c r="HPM25">
+        <v>0.51</v>
+      </c>
+      <c r="HPN25">
+        <v>0.13</v>
+      </c>
+      <c r="HPO25">
+        <v>0.01</v>
+      </c>
+      <c r="HPP25">
+        <v>-0.03</v>
+      </c>
+      <c r="HPS25">
+        <v>-0.26</v>
+      </c>
+      <c r="HPT25">
+        <v>-0.11</v>
+      </c>
+      <c r="HPU25">
+        <v>0.05</v>
+      </c>
+      <c r="HPV25">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="HPW25">
+        <v>-0.08</v>
+      </c>
+      <c r="HPY25">
+        <v>-0.06</v>
+      </c>
+      <c r="HPZ25">
+        <v>-0.1</v>
+      </c>
+      <c r="HQA25">
+        <v>-0.15</v>
+      </c>
+      <c r="HQB25">
+        <v>0.3</v>
+      </c>
+      <c r="HQC25">
+        <v>0.1</v>
+      </c>
+      <c r="HQD25">
+        <v>-0.15</v>
+      </c>
+      <c r="HQE25">
+        <v>-0.08</v>
+      </c>
+      <c r="HQF25">
+        <v>-0.15</v>
+      </c>
+      <c r="HQG25">
+        <v>0.05</v>
+      </c>
+      <c r="HQH25">
+        <v>0.22</v>
+      </c>
+      <c r="HQI25">
+        <v>0.49</v>
+      </c>
+      <c r="HQJ25">
+        <v>0.67</v>
+      </c>
+      <c r="HQK25">
+        <v>0.38</v>
+      </c>
+      <c r="HQL25">
+        <v>0.6</v>
+      </c>
+      <c r="HQM25">
+        <v>0.51</v>
+      </c>
+      <c r="HQN25">
+        <v>0.65</v>
+      </c>
+      <c r="HQO25">
+        <v>0.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>45931</v>
+        <v>46054</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0087</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -84355,50 +84404,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0087a</t>
+          <t>0095a</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11218-025-10079-9</t>
+          <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Autonomy support and studentsâ€™ perceived social-emotional competence: predicting parent-reported social-emotional skills</t>
+          <t>Experiental features of volunteering predict changes in college students' social, emotional, and behavioral skills</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>In this study, we investigated perceived social-emotional competence (PSEC) among 373 Australian secondary school students in relation to parent ratings of social-emotional skills, and perceived teacher and parental autonomy support. Using bifactor exploratory structural equation modelling, we examined five dimensions of PSEC (perceived competence for assertiveness, tolerance, social regulation, emotion regulation, and emotional awareness), identifying a global factor and five specific factors. Following that, we employed structural equation modelling to investigate links between these global and specific factors and five parent-reported social-emotional skills: leadership, cultural competence, teamwork, cognitive reappraisal, and capacity for emotional reflection. Global PSEC was associated positively with all skills, whereas the specific factors were, with one exception, each associated with greater parent-rated skill in a corresponding area (e.g., assertiveness with greater leadership skill; emotion awareness with reflective skills). Addressing a second aim of the research, we tested the extent to which students’ perceptions of autonomy support from teachers and parents assessed near the start of a school term were associated with both students’ PSEC and parent-rated skills assessed at the end of the term. Autonomy-supportive parenting was positively associated with global PSEC. Autonomy-supportive teaching was associated with greater levels of two specific factors: perceived competence for assertiveness and social regulation. Together, findings hold relevance to knowledge and efforts aimed at enhancing social-emotional skills among students.</t>
+          <t>Using an exploratory quasi-experimental design, the present research investigated SEB skills as an antecedent and consequence of volunteering in a sample of college students who were either actively volunteering (N = 169) or not (N = 286). Results indicated that more skilled students participated in volunteering, but volunteering, in general, did not predict positive SEB skill change. However, participants who reported interacting with others while volunteering experienced growth in socially relevant skills. Participants who reported positive subjective evaluations of volunteering also experienced growth in several SEB skills. These findings suggest that domain relevant actions, as well as subjective experiences of engaging in those actions, may be critical for positive SEB skill development. Â© 2026 Elsevier Inc.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Social Psychology of Education</t>
+          <t>Journal of Research in Personality</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Collie, Rebecca J. and Ryan, Richard M.</t>
+          <t>Sewell, Madison N. and Napolitano, Christopher M. and Yoon, Heejun and Soto, Christopher John and Roberts, Brent W.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Collie &amp; Ryan</t>
+          <t>Sewell et al.</t>
         </is>
       </c>
       <c r="K26">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>include</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>autonomysupport</t>
+          <t>volunteering; skilldevelopment</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -84406,42 +84460,37 @@
           <t>both</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>rebecca.collie@unsw.edu.au</t>
-        </is>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>https://osf.io/wsvxt/</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>cross</t>
+          <t>long</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="V26">
-        <v>373</v>
+        <v>455</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>school_age</t>
+          <t>young_adult</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -84451,7 +84500,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>bessi_otherReport</t>
+          <t>bessi45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -84461,206 +84510,80 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>TF</t>
-        </is>
-      </c>
-      <c r="YX26">
-        <v>0.71</v>
-      </c>
-      <c r="ZA26">
-        <v>0.45</v>
-      </c>
-      <c r="ACQ26">
-        <v>0.73</v>
-      </c>
-      <c r="HNS26">
-        <v>0.46</v>
-      </c>
-      <c r="HNT26">
-        <v>0.31</v>
-      </c>
-      <c r="HNU26">
-        <v>0.25</v>
-      </c>
-      <c r="HNV26">
-        <v>0.1</v>
-      </c>
-      <c r="HNW26">
-        <v>0.31</v>
-      </c>
-      <c r="HNX26">
-        <v>0.14</v>
-      </c>
-      <c r="HNY26">
-        <v>0.08</v>
-      </c>
-      <c r="HNZ26">
-        <v>0.22</v>
-      </c>
-      <c r="HOA26">
-        <v>0.22</v>
-      </c>
-      <c r="HOB26">
-        <v>0.36</v>
-      </c>
-      <c r="HOC26">
-        <v>0.32</v>
-      </c>
-      <c r="HOD26">
-        <v>0.25</v>
-      </c>
-      <c r="HOE26">
-        <v>0.47</v>
-      </c>
-      <c r="HOF26">
-        <v>0.05</v>
-      </c>
-      <c r="HOG26">
-        <v>0.13</v>
-      </c>
-      <c r="HOH26">
-        <v>0.13</v>
-      </c>
-      <c r="HOI26">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="HOJ26">
-        <v>0.12</v>
-      </c>
-      <c r="HOK26">
-        <v>0.35</v>
-      </c>
-      <c r="HOL26">
-        <v>0.41</v>
-      </c>
-      <c r="HOM26">
-        <v>0.52</v>
-      </c>
-      <c r="HON26">
-        <v>0.39</v>
-      </c>
-      <c r="HOO26">
-        <v>0.42</v>
-      </c>
-      <c r="HOU26">
-        <v>0.59</v>
-      </c>
-      <c r="HOV26">
-        <v>0.5</v>
-      </c>
-      <c r="HOW26">
-        <v>0.72</v>
-      </c>
-      <c r="HOX26">
-        <v>0.63</v>
-      </c>
-      <c r="HOY26">
-        <v>0.65</v>
-      </c>
-      <c r="HPD26">
-        <v>0.37</v>
-      </c>
-      <c r="HPE26">
-        <v>0.04</v>
-      </c>
-      <c r="HPF26">
-        <v>0.12</v>
-      </c>
-      <c r="HPG26">
-        <v>0.09</v>
-      </c>
-      <c r="HPH26">
-        <v>-0.01</v>
-      </c>
-      <c r="HPL26">
-        <v>-0.05</v>
-      </c>
-      <c r="HPM26">
-        <v>0.51</v>
-      </c>
-      <c r="HPN26">
-        <v>0.13</v>
-      </c>
-      <c r="HPO26">
-        <v>0.01</v>
-      </c>
-      <c r="HPP26">
-        <v>-0.03</v>
-      </c>
-      <c r="HPS26">
-        <v>-0.26</v>
-      </c>
-      <c r="HPT26">
-        <v>-0.11</v>
-      </c>
-      <c r="HPU26">
-        <v>0.05</v>
-      </c>
-      <c r="HPV26">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="HPW26">
-        <v>-0.08</v>
-      </c>
-      <c r="HPY26">
-        <v>-0.06</v>
-      </c>
-      <c r="HPZ26">
-        <v>-0.1</v>
-      </c>
-      <c r="HQA26">
-        <v>-0.15</v>
-      </c>
-      <c r="HQB26">
-        <v>0.3</v>
-      </c>
-      <c r="HQC26">
-        <v>0.1</v>
-      </c>
-      <c r="HQD26">
-        <v>-0.15</v>
-      </c>
-      <c r="HQE26">
-        <v>-0.08</v>
-      </c>
-      <c r="HQF26">
-        <v>-0.15</v>
-      </c>
-      <c r="HQG26">
-        <v>0.05</v>
-      </c>
-      <c r="HQH26">
-        <v>0.22</v>
-      </c>
-      <c r="HQI26">
-        <v>0.49</v>
-      </c>
-      <c r="HQJ26">
-        <v>0.67</v>
-      </c>
-      <c r="HQK26">
-        <v>0.38</v>
-      </c>
-      <c r="HQL26">
-        <v>0.6</v>
-      </c>
-      <c r="HQM26">
-        <v>0.51</v>
-      </c>
-      <c r="HQN26">
-        <v>0.65</v>
-      </c>
-      <c r="HQO26">
-        <v>0.68</v>
+          <t>Gerardo</t>
+        </is>
+      </c>
+      <c r="AF26">
+        <v>0.3330224193081219</v>
+      </c>
+      <c r="AG26">
+        <v>0.4596512270598077</v>
+      </c>
+      <c r="AH26">
+        <v>0.5320576831334216</v>
+      </c>
+      <c r="AI26">
+        <v>0.3242378668410512</v>
+      </c>
+      <c r="AZ26">
+        <v>0.4979522039905168</v>
+      </c>
+      <c r="BA26">
+        <v>0.3652453106055803</v>
+      </c>
+      <c r="BB26">
+        <v>0.387208368782807</v>
+      </c>
+      <c r="BS26">
+        <v>0.4613724415274998</v>
+      </c>
+      <c r="BT26">
+        <v>0.4106499312594121</v>
+      </c>
+      <c r="CK26">
+        <v>0.3478894084815676</v>
+      </c>
+      <c r="JN26">
+        <v>0.04455123620056217</v>
+      </c>
+      <c r="JO26">
+        <v>0.07530718858853158</v>
+      </c>
+      <c r="JP26">
+        <v>0.1418991528525441</v>
+      </c>
+      <c r="JQ26">
+        <v>0.02259557439649528</v>
+      </c>
+      <c r="JR26">
+        <v>-0.1812978912538156</v>
+      </c>
+      <c r="DLS26">
+        <v>-0.05125524187103325</v>
+      </c>
+      <c r="DMM26">
+        <v>0.2646806101192998</v>
+      </c>
+      <c r="DNA26">
+        <v>0.07878029097361108</v>
+      </c>
+      <c r="DNO26">
+        <v>0.1666545203436967</v>
+      </c>
+      <c r="DOC26">
+        <v>0.1772218757143176</v>
+      </c>
+      <c r="DOQ26">
+        <v>0.115134156294775</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>45931</v>
+        <v>46082</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0087</t>
+          <t>0100</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -84670,50 +84593,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0087a</t>
+          <t>0100a</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s11218-025-10079-9</t>
+          <t>https://doi.org/10.1177/00222194261417592</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Autonomy support and studentsâ€™ perceived social-emotional competence: predicting parent-reported social-emotional skills</t>
+          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>In this study, we investigated perceived social-emotional competence (PSEC) among 373 Australian secondary school students in relation to parent ratings of social-emotional skills, and perceived teacher and parental autonomy support. Using bifactor exploratory structural equation modelling, we examined five dimensions of PSEC (perceived competence for assertiveness, tolerance, social regulation, emotion regulation, and emotional awareness), identifying a global factor and five specific factors. Following that, we employed structural equation modelling to investigate links between these global and specific factors and five parent-reported social-emotional skills: leadership, cultural competence, teamwork, cognitive reappraisal, and capacity for emotional reflection. Global PSEC was associated positively with all skills, whereas the specific factors were, with one exception, each associated with greater parent-rated skill in a corresponding area (e.g., assertiveness with greater leadership skill; emotion awareness with reflective skills). Addressing a second aim of the research, we tested the extent to which students’ perceptions of autonomy support from teachers and parents assessed near the start of a school term were associated with both students’ PSEC and parent-rated skills assessed at the end of the term. Autonomy-supportive parenting was positively associated with global PSEC. Autonomy-supportive teaching was associated with greater levels of two specific factors: perceived competence for assertiveness and social regulation. Together, findings hold relevance to knowledge and efforts aimed at enhancing social-emotional skills among students.</t>
+          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Social Psychology of Education</t>
+          <t>JOURNAL OF LEARNING DISABILITIES</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Collie, Rebecca J. and Ryan, Richard M.</t>
+          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Collie &amp; Ryan</t>
+          <t>Pellegrino et al.</t>
         </is>
       </c>
       <c r="K27">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>include</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>autonomysupport</t>
+          <t>academicachievement; schoolsatisfaction; disabilities</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -84723,12 +84651,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>rebecca.collie@unsw.edu.au</t>
+          <t>gerardo.pellegrino@phd.unipd.it</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>https://osf.io/69q84/</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -84738,35 +84666,40 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>82</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="V27">
-        <v>373</v>
+        <v>752</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>school_age</t>
+          <t>young_adult</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>not_clinical</t>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>learning disabilities</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>bessi_otherReport</t>
+          <t>bessi45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -84779,752 +84712,238 @@
           <t>TF</t>
         </is>
       </c>
-      <c r="YX27">
-        <v>0.71</v>
-      </c>
-      <c r="ZA27">
-        <v>0.45</v>
-      </c>
-      <c r="ACQ27">
-        <v>0.73</v>
-      </c>
-      <c r="HNS27">
-        <v>0.46</v>
-      </c>
-      <c r="HNT27">
-        <v>0.31</v>
-      </c>
-      <c r="HNU27">
-        <v>0.25</v>
-      </c>
-      <c r="HNV27">
-        <v>0.1</v>
-      </c>
-      <c r="HNW27">
-        <v>0.31</v>
-      </c>
-      <c r="HNX27">
-        <v>0.14</v>
-      </c>
-      <c r="HNY27">
-        <v>0.08</v>
-      </c>
-      <c r="HNZ27">
-        <v>0.22</v>
-      </c>
-      <c r="HOA27">
-        <v>0.22</v>
-      </c>
-      <c r="HOB27">
-        <v>0.36</v>
-      </c>
-      <c r="HOC27">
-        <v>0.32</v>
-      </c>
-      <c r="HOD27">
-        <v>0.25</v>
-      </c>
-      <c r="HOE27">
-        <v>0.47</v>
-      </c>
-      <c r="HOF27">
-        <v>0.05</v>
-      </c>
-      <c r="HOG27">
-        <v>0.13</v>
-      </c>
-      <c r="HOH27">
-        <v>0.13</v>
-      </c>
-      <c r="HOI27">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="HOJ27">
-        <v>0.12</v>
-      </c>
-      <c r="HOK27">
-        <v>0.35</v>
-      </c>
-      <c r="HOL27">
-        <v>0.41</v>
-      </c>
-      <c r="HOM27">
-        <v>0.52</v>
-      </c>
-      <c r="HON27">
-        <v>0.39</v>
-      </c>
-      <c r="HOO27">
-        <v>0.42</v>
-      </c>
-      <c r="HOU27">
-        <v>0.59</v>
-      </c>
-      <c r="HOV27">
-        <v>0.5</v>
-      </c>
-      <c r="HOW27">
-        <v>0.72</v>
-      </c>
-      <c r="HOX27">
-        <v>0.63</v>
-      </c>
-      <c r="HOY27">
-        <v>0.65</v>
-      </c>
-      <c r="HPD27">
-        <v>0.37</v>
-      </c>
-      <c r="HPE27">
-        <v>0.04</v>
-      </c>
-      <c r="HPF27">
-        <v>0.12</v>
-      </c>
-      <c r="HPG27">
-        <v>0.09</v>
-      </c>
-      <c r="HPH27">
-        <v>-0.01</v>
-      </c>
-      <c r="HPL27">
-        <v>-0.05</v>
-      </c>
-      <c r="HPM27">
-        <v>0.51</v>
-      </c>
-      <c r="HPN27">
-        <v>0.13</v>
-      </c>
-      <c r="HPO27">
-        <v>0.01</v>
-      </c>
-      <c r="HPP27">
-        <v>-0.03</v>
-      </c>
-      <c r="HPS27">
-        <v>-0.26</v>
-      </c>
-      <c r="HPT27">
-        <v>-0.11</v>
-      </c>
-      <c r="HPU27">
-        <v>0.05</v>
-      </c>
-      <c r="HPV27">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="HPW27">
-        <v>-0.08</v>
-      </c>
-      <c r="HPY27">
-        <v>-0.06</v>
-      </c>
-      <c r="HPZ27">
-        <v>-0.1</v>
-      </c>
-      <c r="HQA27">
-        <v>-0.15</v>
-      </c>
-      <c r="HQB27">
-        <v>0.3</v>
-      </c>
-      <c r="HQC27">
-        <v>0.1</v>
-      </c>
-      <c r="HQD27">
-        <v>-0.15</v>
-      </c>
-      <c r="HQE27">
-        <v>-0.08</v>
-      </c>
-      <c r="HQF27">
-        <v>-0.15</v>
-      </c>
-      <c r="HQG27">
-        <v>0.05</v>
-      </c>
-      <c r="HQH27">
-        <v>0.22</v>
-      </c>
-      <c r="HQI27">
-        <v>0.49</v>
-      </c>
-      <c r="HQJ27">
-        <v>0.67</v>
-      </c>
-      <c r="HQK27">
-        <v>0.38</v>
-      </c>
-      <c r="HQL27">
-        <v>0.6</v>
-      </c>
-      <c r="HQM27">
-        <v>0.51</v>
-      </c>
-      <c r="HQN27">
-        <v>0.65</v>
-      </c>
-      <c r="HQO27">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2">
-        <v>46054</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0095</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0095a</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Experiental features of volunteering predict changes in college students' social, emotional, and behavioral skills</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Using an exploratory quasi-experimental design, the present research investigated SEB skills as an antecedent and consequence of volunteering in a sample of college students who were either actively volunteering (N = 169) or not (N = 286). Results indicated that more skilled students participated in volunteering, but volunteering, in general, did not predict positive SEB skill change. However, participants who reported interacting with others while volunteering experienced growth in socially relevant skills. Participants who reported positive subjective evaluations of volunteering also experienced growth in several SEB skills. These findings suggest that domain relevant actions, as well as subjective experiences of engaging in those actions, may be critical for positive SEB skill development. Â© 2026 Elsevier Inc.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Journal of Research in Personality</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sewell, Madison N. and Napolitano, Christopher M. and Yoon, Heejun and Soto, Christopher John and Roberts, Brent W.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Sewell et al.</t>
-        </is>
-      </c>
-      <c r="K28">
-        <v>2026</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>volunteering; skilldevelopment</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>https://osf.io/wsvxt/</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="V28">
-        <v>455</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>young_adult</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>not_clinical</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>bessi45</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gerardo</t>
-        </is>
-      </c>
-      <c r="AF28">
-        <v>0.3330224193081219</v>
-      </c>
-      <c r="AG28">
-        <v>0.4596512270598077</v>
-      </c>
-      <c r="AH28">
-        <v>0.5320576831334216</v>
-      </c>
-      <c r="AI28">
-        <v>0.3242378668410512</v>
-      </c>
-      <c r="AZ28">
-        <v>0.4979522039905168</v>
-      </c>
-      <c r="BA28">
-        <v>0.3652453106055803</v>
-      </c>
-      <c r="BB28">
-        <v>0.387208368782807</v>
-      </c>
-      <c r="BS28">
-        <v>0.4613724415274998</v>
-      </c>
-      <c r="BT28">
-        <v>0.4106499312594121</v>
-      </c>
-      <c r="CK28">
-        <v>0.3478894084815676</v>
-      </c>
-      <c r="JN28">
-        <v>0.04455123620056217</v>
-      </c>
-      <c r="JO28">
-        <v>0.07530718858853158</v>
-      </c>
-      <c r="JP28">
-        <v>0.1418991528525441</v>
-      </c>
-      <c r="JQ28">
-        <v>0.02259557439649528</v>
-      </c>
-      <c r="JR28">
-        <v>-0.1812978912538156</v>
-      </c>
-      <c r="DLS28">
-        <v>-0.05125524187103325</v>
-      </c>
-      <c r="DMM28">
-        <v>0.2646806101192998</v>
-      </c>
-      <c r="DNA28">
-        <v>0.07878029097361108</v>
-      </c>
-      <c r="DNO28">
-        <v>0.1666545203436967</v>
-      </c>
-      <c r="DOC28">
-        <v>0.1772218757143176</v>
-      </c>
-      <c r="DOQ28">
-        <v>0.115134156294775</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2">
-        <v>46082</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0100</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0100a</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1177/00222194261417592</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>JOURNAL OF LEARNING DISABILITIES</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Pellegrino et al.</t>
-        </is>
-      </c>
-      <c r="K29">
-        <v>2026</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>include</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>academicachievement; schoolsatisfaction; disabilities</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>gerardo.pellegrino@phd.unipd.it</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>https://osf.io/69q84/</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>cross</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="V29">
-        <v>752</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>young_adult</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>clinical</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>learning disabilities</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>bessi45</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>TF</t>
-        </is>
-      </c>
-      <c r="AF29">
+      <c r="AF27">
         <v>0.3897922881894729</v>
       </c>
-      <c r="AG29">
+      <c r="AG27">
         <v>0.4343885218477122</v>
       </c>
-      <c r="AH29">
+      <c r="AH27">
         <v>0.365121009514038</v>
       </c>
-      <c r="AI29">
+      <c r="AI27">
         <v>0.2636812289743455</v>
       </c>
-      <c r="AO29">
+      <c r="AO27">
         <v>0.4573981796399659</v>
       </c>
-      <c r="AP29">
+      <c r="AP27">
         <v>0.2150884111587807</v>
       </c>
-      <c r="AY29">
+      <c r="AY27">
         <v>0.309149417263011</v>
       </c>
-      <c r="AZ29">
+      <c r="AZ27">
         <v>0.5658514819150465</v>
       </c>
-      <c r="BA29">
+      <c r="BA27">
         <v>0.4043396359654297</v>
       </c>
-      <c r="BB29">
+      <c r="BB27">
         <v>0.4387692360844135</v>
       </c>
-      <c r="BH29">
+      <c r="BH27">
         <v>0.3772889514539913</v>
       </c>
-      <c r="BI29">
+      <c r="BI27">
         <v>0.08903509188091555</v>
       </c>
-      <c r="BR29">
+      <c r="BR27">
         <v>0.3542830877811803</v>
       </c>
-      <c r="BS29">
+      <c r="BS27">
         <v>0.5126122080478571</v>
       </c>
-      <c r="BT29">
+      <c r="BT27">
         <v>0.3822180284555047</v>
       </c>
-      <c r="BZ29">
+      <c r="BZ27">
         <v>0.4067922354760057</v>
       </c>
-      <c r="CA29">
+      <c r="CA27">
         <v>0.1223279872174429</v>
       </c>
-      <c r="CJ29">
+      <c r="CJ27">
         <v>0.2629075583679749</v>
       </c>
-      <c r="CK29">
+      <c r="CK27">
         <v>0.3565627585032196</v>
       </c>
-      <c r="CQ29">
+      <c r="CQ27">
         <v>0.3184101560380294</v>
       </c>
-      <c r="CR29">
+      <c r="CR27">
         <v>0.06861347542171189</v>
       </c>
-      <c r="DA29">
+      <c r="DA27">
         <v>0.4503350402683908</v>
       </c>
-      <c r="DG29">
+      <c r="DG27">
         <v>0.2153874357713632</v>
       </c>
-      <c r="DH29">
+      <c r="DH27">
         <v>-0.007065551422642442</v>
       </c>
-      <c r="DQ29">
+      <c r="DQ27">
         <v>0.1375828062149693</v>
       </c>
-      <c r="GE29">
+      <c r="GE27">
         <v>0.201815379344535</v>
       </c>
-      <c r="GN29">
+      <c r="GN27">
         <v>0.4657733418003734</v>
       </c>
-      <c r="GW29">
+      <c r="GW27">
         <v>0.07828991508347706</v>
       </c>
-      <c r="JN29">
+      <c r="JN27">
         <v>0.1093216055628479</v>
       </c>
-      <c r="JO29">
+      <c r="JO27">
         <v>-0.08373713535117611</v>
       </c>
-      <c r="JP29">
+      <c r="JP27">
         <v>0.07883443083303709</v>
       </c>
-      <c r="JQ29">
+      <c r="JQ27">
         <v>-0.04096254386167063</v>
       </c>
-      <c r="JR29">
+      <c r="JR27">
         <v>-0.164617946223372</v>
       </c>
-      <c r="JS29">
+      <c r="JS27">
         <v>0.03661715191468676</v>
       </c>
-      <c r="JT29">
+      <c r="JT27">
         <v>0.1761651852528344</v>
       </c>
-      <c r="DWY29">
+      <c r="DWY27">
         <v>0.1691472847032733</v>
       </c>
-      <c r="HKD29">
+      <c r="HKD27">
         <v>0.5190585096777481</v>
       </c>
-      <c r="HKF29">
+      <c r="HKF27">
         <v>0.5175109381568147</v>
       </c>
-      <c r="HKH29">
+      <c r="HKH27">
         <v>0.2173495938924325</v>
       </c>
-      <c r="HKJ29">
+      <c r="HKJ27">
         <v>0.2231156696041342</v>
       </c>
-      <c r="HKL29">
+      <c r="HKL27">
         <v>0.308283191116604</v>
       </c>
-      <c r="HKN29">
+      <c r="HKN27">
         <v>0.2420030344806121</v>
       </c>
-      <c r="HKQ29">
+      <c r="HKQ27">
         <v>0.1020337966898319</v>
       </c>
-      <c r="HLI29">
+      <c r="HLI27">
         <v>0.06298995314517195</v>
       </c>
-      <c r="HLM29">
+      <c r="HLM27">
         <v>0.5659781083300155</v>
       </c>
-      <c r="HLQ29">
+      <c r="HLQ27">
         <v>0.3133153878823099</v>
       </c>
-      <c r="HLU29">
+      <c r="HLU27">
         <v>0.3128176562091499</v>
       </c>
-      <c r="HLY29">
+      <c r="HLY27">
         <v>0.3487956190236833</v>
       </c>
-      <c r="HMC29">
+      <c r="HMC27">
         <v>0.31658358416447</v>
       </c>
-      <c r="HMO29">
+      <c r="HMO27">
         <v>0.3074950168848075</v>
       </c>
-      <c r="HMQ29">
+      <c r="HMQ27">
         <v>0.5312753669005742</v>
       </c>
-      <c r="HND29">
+      <c r="HND27">
         <v>0.2772002425663024</v>
       </c>
-      <c r="HNH29">
+      <c r="HNH27">
         <v>0.259628994844297</v>
       </c>
-      <c r="HNJ29">
+      <c r="HNJ27">
         <v>0.303601934935523</v>
       </c>
-      <c r="HNK29">
+      <c r="HNK27">
         <v>0.3005495330136056</v>
       </c>
-      <c r="HNL29">
+      <c r="HNL27">
         <v>0.2756542090471613</v>
       </c>
-      <c r="HNM29">
+      <c r="HNM27">
         <v>0.2156124607101731</v>
       </c>
-      <c r="HNN29">
+      <c r="HNN27">
         <v>0.2826184237158135</v>
       </c>
-      <c r="HNO29">
+      <c r="HNO27">
         <v>0.2769187898730788</v>
       </c>
-      <c r="HNP29">
+      <c r="HNP27">
         <v>0.2309571978689031</v>
       </c>
-      <c r="HNQ29">
+      <c r="HNQ27">
         <v>0.1112902803236752</v>
       </c>
-      <c r="HNR29">
+      <c r="HNR27">
         <v>0.0003824779547645992</v>
       </c>
-      <c r="HQP29">
+      <c r="HQP27">
         <v>-0.1192946976461384</v>
       </c>
-      <c r="HQQ29">
+      <c r="HQQ27">
         <v>0.05242883361164581</v>
       </c>
-      <c r="HQR29">
+      <c r="HQR27">
         <v>-0.2766343722339456</v>
       </c>
-      <c r="HQS29">
+      <c r="HQS27">
         <v>-0.1814312710539319</v>
       </c>
-      <c r="HQT29">
+      <c r="HQT27">
         <v>-0.1694009206403628</v>
       </c>
-      <c r="HQU29">
+      <c r="HQU27">
         <v>-0.2209096192298554</v>
       </c>
-      <c r="HQV29">
+      <c r="HQV27">
         <v>-0.3855928647410115</v>
       </c>
-      <c r="HQW29">
+      <c r="HQW27">
         <v>0.4612713330315539</v>
       </c>
-      <c r="HQX29">
+      <c r="HQX27">
         <v>0.4425697766589992</v>
       </c>
-      <c r="HQY29">
+      <c r="HQY27">
         <v>0.5520892997190852</v>
       </c>
-      <c r="HQZ29">
+      <c r="HQZ27">
         <v>-0.4757545371340873</v>
       </c>
-      <c r="HRA29">
+      <c r="HRA27">
         <v>-0.3750050994964406</v>
       </c>
-      <c r="HRB29">
+      <c r="HRB27">
         <v>-0.2988773805863365</v>
       </c>
-      <c r="HRC29">
+      <c r="HRC27">
         <v>0.3736792622798559</v>
       </c>
-      <c r="HRD29">
+      <c r="HRD27">
         <v>-0.4597814935732237</v>
       </c>
-      <c r="HRE29">
+      <c r="HRE27">
         <v>-0.4130474373501075</v>
       </c>
     </row>
